--- a/backtest_sonuclari_v2.xlsx
+++ b/backtest_sonuclari_v2.xlsx
@@ -487,25 +487,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.54</v>
+        <v>49.08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="D2" t="n">
-        <v>27.39</v>
+        <v>13.04</v>
       </c>
       <c r="E2" t="n">
-        <v>2204.73</v>
+        <v>152.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>46.43</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -515,25 +515,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.03</v>
+        <v>51.19</v>
       </c>
       <c r="C3" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="D3" t="n">
-        <v>11.42</v>
+        <v>15.49</v>
       </c>
       <c r="E3" t="n">
-        <v>2025.62</v>
+        <v>1250.77</v>
       </c>
       <c r="F3" t="n">
-        <v>8.279999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>54.29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -543,25 +543,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.02</v>
+        <v>46.21</v>
       </c>
       <c r="C4" t="n">
-        <v>3.13</v>
+        <v>5.25</v>
       </c>
       <c r="D4" t="n">
-        <v>14.22</v>
+        <v>20.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1019.53</v>
+        <v>2112.88</v>
       </c>
       <c r="F4" t="n">
-        <v>8.279999999999999</v>
+        <v>5.05</v>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>45.61</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="5">
@@ -571,25 +571,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.71</v>
+        <v>52.08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.31</v>
+        <v>6.72</v>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>14.32</v>
       </c>
       <c r="E5" t="n">
-        <v>1785.17</v>
+        <v>188.03</v>
       </c>
       <c r="F5" t="n">
-        <v>15.39</v>
+        <v>5.76</v>
       </c>
       <c r="G5" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>42.27</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="6">
@@ -599,25 +599,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52.78</v>
+        <v>51.24</v>
       </c>
       <c r="C6" t="n">
-        <v>6.94</v>
+        <v>2.48</v>
       </c>
       <c r="D6" t="n">
-        <v>15.42</v>
+        <v>11.51</v>
       </c>
       <c r="E6" t="n">
-        <v>1656.29</v>
+        <v>-24.9</v>
       </c>
       <c r="F6" t="n">
-        <v>10.14</v>
+        <v>11.46</v>
       </c>
       <c r="G6" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>56.18</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="7">
@@ -627,25 +627,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45.96</v>
+        <v>47.07</v>
       </c>
       <c r="C7" t="n">
-        <v>13.71</v>
+        <v>4.35</v>
       </c>
       <c r="D7" t="n">
-        <v>15.12</v>
+        <v>10.82</v>
       </c>
       <c r="E7" t="n">
-        <v>10802.86</v>
+        <v>441.44</v>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>3.26</v>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>79.59</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
@@ -655,25 +655,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48.21</v>
+        <v>47.49</v>
       </c>
       <c r="C8" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="D8" t="n">
-        <v>12.84</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="n">
-        <v>510.84</v>
+        <v>681.46</v>
       </c>
       <c r="F8" t="n">
-        <v>23.6</v>
+        <v>7.95</v>
       </c>
       <c r="G8" t="n">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>52.87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -683,25 +683,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53.87</v>
+        <v>48.56</v>
       </c>
       <c r="C9" t="n">
-        <v>8.35</v>
+        <v>5.23</v>
       </c>
       <c r="D9" t="n">
-        <v>17.09</v>
+        <v>11.47</v>
       </c>
       <c r="E9" t="n">
-        <v>3366.84</v>
+        <v>3944.73</v>
       </c>
       <c r="F9" t="n">
-        <v>7.12</v>
+        <v>10.78</v>
       </c>
       <c r="G9" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="H9" t="n">
-        <v>54.84</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="10">
@@ -711,25 +711,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56.53</v>
+        <v>51.61</v>
       </c>
       <c r="C10" t="n">
-        <v>31.64</v>
+        <v>4.18</v>
       </c>
       <c r="D10" t="n">
-        <v>15.5</v>
+        <v>17.22</v>
       </c>
       <c r="E10" t="n">
-        <v>529.77</v>
+        <v>1119.97</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6</v>
+        <v>6.38</v>
       </c>
       <c r="G10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>46.81</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="11">
@@ -739,25 +739,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49.09</v>
+        <v>52.74</v>
       </c>
       <c r="C11" t="n">
-        <v>6.35</v>
+        <v>2.54</v>
       </c>
       <c r="D11" t="n">
-        <v>12.94</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="n">
-        <v>7994.34</v>
+        <v>7556.01</v>
       </c>
       <c r="F11" t="n">
-        <v>21.4</v>
+        <v>3.73</v>
       </c>
       <c r="G11" t="n">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>49.44</v>
+        <v>62.34</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_sonuclari_v2.xlsx
+++ b/backtest_sonuclari_v2.xlsx
@@ -487,25 +487,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.08</v>
+        <v>52.48</v>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
+        <v>0.79</v>
       </c>
       <c r="D2" t="n">
-        <v>13.04</v>
+        <v>16.57</v>
       </c>
       <c r="E2" t="n">
-        <v>152.8</v>
+        <v>-53.52</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="3">
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.19</v>
+        <v>51.22</v>
       </c>
       <c r="C3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="D3" t="n">
-        <v>15.49</v>
+        <v>13.56</v>
       </c>
       <c r="E3" t="n">
         <v>1250.77</v>
@@ -543,25 +543,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.21</v>
+        <v>46.2</v>
       </c>
       <c r="C4" t="n">
-        <v>5.25</v>
+        <v>6.11</v>
       </c>
       <c r="D4" t="n">
-        <v>20.35</v>
+        <v>8.98</v>
       </c>
       <c r="E4" t="n">
-        <v>2112.88</v>
+        <v>2213.51</v>
       </c>
       <c r="F4" t="n">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="G4" t="n">
         <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>51.11</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="5">
@@ -571,25 +571,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.08</v>
+        <v>48.69</v>
       </c>
       <c r="C5" t="n">
-        <v>6.72</v>
+        <v>19.19</v>
       </c>
       <c r="D5" t="n">
-        <v>14.32</v>
+        <v>21.03</v>
       </c>
       <c r="E5" t="n">
-        <v>188.03</v>
+        <v>422.79</v>
       </c>
       <c r="F5" t="n">
-        <v>5.76</v>
+        <v>12.94</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="H5" t="n">
-        <v>42.86</v>
+        <v>39.13</v>
       </c>
     </row>
     <row r="6">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.24</v>
+        <v>51.25</v>
       </c>
       <c r="C6" t="n">
-        <v>2.48</v>
+        <v>9.16</v>
       </c>
       <c r="D6" t="n">
-        <v>11.51</v>
+        <v>17.41</v>
       </c>
       <c r="E6" t="n">
         <v>-24.9</v>
@@ -627,25 +627,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.07</v>
+        <v>48.49</v>
       </c>
       <c r="C7" t="n">
-        <v>4.35</v>
+        <v>0.52</v>
       </c>
       <c r="D7" t="n">
-        <v>10.82</v>
+        <v>13.89</v>
       </c>
       <c r="E7" t="n">
-        <v>441.44</v>
+        <v>219.92</v>
       </c>
       <c r="F7" t="n">
-        <v>3.26</v>
+        <v>0.97</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>41.67</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="8">
@@ -658,10 +658,10 @@
         <v>47.49</v>
       </c>
       <c r="C8" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.18</v>
       </c>
       <c r="E8" t="n">
         <v>681.46</v>
@@ -683,25 +683,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48.56</v>
+        <v>48.57</v>
       </c>
       <c r="C9" t="n">
-        <v>5.23</v>
+        <v>5.81</v>
       </c>
       <c r="D9" t="n">
-        <v>11.47</v>
+        <v>17.1</v>
       </c>
       <c r="E9" t="n">
-        <v>3944.73</v>
+        <v>3970.13</v>
       </c>
       <c r="F9" t="n">
-        <v>10.78</v>
+        <v>11.02</v>
       </c>
       <c r="G9" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H9" t="n">
-        <v>47.57</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="10">
@@ -711,25 +711,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.61</v>
+        <v>51.63</v>
       </c>
       <c r="C10" t="n">
-        <v>4.18</v>
+        <v>8.83</v>
       </c>
       <c r="D10" t="n">
-        <v>17.22</v>
+        <v>15.27</v>
       </c>
       <c r="E10" t="n">
-        <v>1119.97</v>
+        <v>1349.26</v>
       </c>
       <c r="F10" t="n">
-        <v>6.38</v>
+        <v>6.03</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>55.1</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="11">
@@ -739,25 +739,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52.74</v>
+        <v>52.7</v>
       </c>
       <c r="C11" t="n">
-        <v>2.54</v>
+        <v>5.09</v>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.68</v>
       </c>
       <c r="E11" t="n">
-        <v>7556.01</v>
+        <v>7552.17</v>
       </c>
       <c r="F11" t="n">
         <v>3.73</v>
       </c>
       <c r="G11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="n">
-        <v>62.34</v>
+        <v>61.54</v>
       </c>
     </row>
   </sheetData>
